--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.05</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK29"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="21">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45946.75</v>
+        <v>45946.79166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45946.79166666666</v>
+        <v>45946.89583333334</v>
       </c>
     </row>
     <row r="28">
@@ -4102,135 +4102,6 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45946.89583333334</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="n">
         <v>45946.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK28"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.53125</v>
       </c>
     </row>
     <row r="21">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.53125</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>2.64</v>
       </c>
       <c r="M24" t="n">
-        <v>3.53</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>1.53</v>
+        <v>2.49</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.89583333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.64</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.49</v>
+        <v>7.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,264 +3844,6 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45946.79166666666</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="n">
-        <v>45946.89583333334</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="3" t="n">
         <v>45946.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.4375</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.53125</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.53125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45946.79166666666</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45946.89583333334</v>
+        <v>45946.79166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3739,111 +3739,240 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
+        <v>45946.89583333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Fluminense</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Juventude</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>1.45</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>4.4</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>7.3</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>2</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45946.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.53125</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.53125</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.4</v>
+        <v>2.47</v>
       </c>
       <c r="M23" t="n">
-        <v>3.53</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.75</v>
       </c>
     </row>
     <row r="25">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="N27" t="n">
-        <v>7.3</v>
+        <v>2.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3258,34 +3258,34 @@
         <v>1.53</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y22" t="n">
         <v>2.1</v>
@@ -3294,16 +3294,16 @@
         <v>1.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N26" t="n">
-        <v>7.6</v>
+        <v>2.39</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O22" t="n">
-        <v>6.03</v>
+        <v>5.66</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3387,34 +3387,34 @@
         <v>2.47</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Y23" t="n">
         <v>1.8</v>
@@ -3423,16 +3423,16 @@
         <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
         <v>5.58</v>
@@ -708,16 +708,16 @@
         <v>3.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC2" t="n">
         <v>1.83</v>
@@ -739,7 +739,7 @@
         <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.53</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="17">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.53125</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.53125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>1.32</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6</v>
+        <v>6.75</v>
       </c>
       <c r="O22" t="n">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.47</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.21</v>
+        <v>3.53</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>5.66</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="T23" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.94</v>
+        <v>3.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45946.75</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3645,34 +3645,34 @@
         <v>2.49</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y25" t="n">
         <v>2.45</v>
@@ -3681,16 +3681,16 @@
         <v>1.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.34</v>
       </c>
-      <c r="M27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>4.53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9</v>
+        <v>4.05</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.53</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.53125</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.75</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>6.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.53125</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.32</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>6.75</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.4</v>
+        <v>2.47</v>
       </c>
       <c r="M23" t="n">
-        <v>3.53</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="O23" t="n">
-        <v>5.66</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.75</v>
       </c>
     </row>
     <row r="25">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="O25" t="n">
         <v>3.4</v>
@@ -3666,7 +3666,7 @@
         <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W25" t="n">
         <v>1.51</v>
@@ -3675,10 +3675,10 @@
         <v>2.44</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AA25" t="n">
         <v>5.13</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.34</v>
       </c>
-      <c r="M26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>7</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.92</v>
+        <v>1.41</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.01</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.39</v>
+        <v>8.5</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>1.89</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T27" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.81</v>
+        <v>3.62</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.41</v>
+        <v>2.92</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45946.42013888889</v>
+        <v>45946.42361111111</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.42013888889</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.42361111111</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.53125</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.75</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>2.64</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>1.53</v>
+        <v>2.49</v>
       </c>
       <c r="O22" t="n">
-        <v>5.66</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.37</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.21</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.21</v>
       </c>
-      <c r="X23" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.46</v>
+        <v>2.92</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.89583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,393 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45946.75</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45946.79166666666</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
-        <v>45946.89583333334</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45946</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="n">
         <v>45946.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.58</v>
+        <v>5.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.35</v>
@@ -702,22 +702,22 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
         <v>3.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC2" t="n">
         <v>1.83</v>
@@ -739,7 +739,7 @@
         <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="O9" t="n">
         <v>2.55</v>
@@ -1596,7 +1596,7 @@
         <v>3.58</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
         <v>1.63</v>
@@ -1605,19 +1605,19 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
         <v>2.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
         <v>1.62</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.53</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.53</v>
+        <v>6.75</v>
       </c>
       <c r="O19" t="n">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.52</v>
+        <v>1.66</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>5.34</v>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X20" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.75</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="R22" t="n">
         <v>1.52</v>
@@ -3273,37 +3273,37 @@
         <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.13</v>
+        <v>5.1</v>
       </c>
       <c r="AB22" t="n">
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>1.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
         <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T23" t="n">
         <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="M24" t="n">
-        <v>3.01</v>
+        <v>3.17</v>
       </c>
       <c r="N24" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="O24" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
@@ -3540,28 +3540,28 @@
         <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="Y24" t="n">
         <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.81</v>
+        <v>3.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.34</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N20" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="O20" t="n">
         <v>5.34</v>
@@ -3027,16 +3027,16 @@
         <v>1.24</v>
       </c>
       <c r="X20" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AB20" t="n">
         <v>1.3</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>3.2</v>
@@ -3162,7 +3162,7 @@
         <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>2.94</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="O22" t="n">
         <v>3.6</v>
@@ -3282,19 +3282,19 @@
         <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AB22" t="n">
         <v>1.13</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>2.39</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X23" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.92</v>
+        <v>1.43</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.78</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.17</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.61</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.12</v>
+        <v>7.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.43</v>
+        <v>2.92</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -672,13 +672,13 @@
         <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
         <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="P2" t="n">
         <v>2.2</v>
@@ -702,7 +702,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
         <v>3.42</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3000,7 +3000,7 @@
         <v>1.53</v>
       </c>
       <c r="O20" t="n">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
         <v>2.19</v>
@@ -3036,10 +3036,10 @@
         <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC20" t="n">
         <v>1.82</v>
@@ -3129,28 +3129,28 @@
         <v>2.47</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
         <v>1.21</v>
@@ -3171,10 +3171,10 @@
         <v>1.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3258,25 +3258,25 @@
         <v>2.49</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
         <v>1.06</v>
@@ -3300,7 +3300,7 @@
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AD22" t="n">
         <v>1.69</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3429,10 +3429,10 @@
         <v>1.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3516,34 +3516,34 @@
         <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="Y24" t="n">
         <v>1.94</v>
@@ -3552,16 +3552,16 @@
         <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="P23" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.45</v>
+        <v>3.08</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>2.39</v>
       </c>
       <c r="O24" t="n">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3.12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.08</v>
+        <v>1.45</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3000,13 +3000,13 @@
         <v>1.53</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="P20" t="n">
         <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="R20" t="n">
         <v>1.36</v>
@@ -3036,16 +3036,16 @@
         <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3150,13 +3150,13 @@
         <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>3.62</v>
+        <v>4.06</v>
       </c>
       <c r="Y21" t="n">
         <v>1.8</v>
@@ -3165,10 +3165,10 @@
         <v>1.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC21" t="n">
         <v>1.7</v>
@@ -3258,25 +3258,25 @@
         <v>2.49</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
         <v>1.06</v>
@@ -3300,10 +3300,10 @@
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
         <v>1.41</v>
@@ -3558,10 +3558,10 @@
         <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="P2" t="n">
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.53</v>
+        <v>5.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.4</v>
+        <v>5.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.53</v>
+        <v>3.78</v>
       </c>
       <c r="N20" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>5.27</v>
+        <v>4.36</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="R20" t="n">
         <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
         <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X20" t="n">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
         <v>3.1</v>
@@ -3138,31 +3138,31 @@
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>4.06</v>
+        <v>3.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AA21" t="n">
         <v>2.89</v>
@@ -3171,10 +3171,10 @@
         <v>1.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.34</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH23" t="n">
-        <v>3.08</v>
+        <v>1.43</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="P24" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.12</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.43</v>
+        <v>3.08</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="N22" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
         <v>1.52</v>
@@ -3282,16 +3282,16 @@
         <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X22" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
         <v>4.6</v>
@@ -3300,10 +3300,10 @@
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.01</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.43</v>
+        <v>3.17</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>2.87</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>2.59</v>
       </c>
       <c r="O24" t="n">
-        <v>1.84</v>
+        <v>3.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3.24</v>
       </c>
       <c r="R24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.39</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH24" t="n">
-        <v>3.08</v>
+        <v>1.43</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>5.14</v>
       </c>
       <c r="N13" t="n">
-        <v>2.87</v>
+        <v>8.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>9.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45946.5</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.57</v>
+        <v>4.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O20" t="n">
-        <v>4.36</v>
+        <v>5.05</v>
       </c>
       <c r="P20" t="n">
         <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="R20" t="n">
         <v>1.36</v>
@@ -3015,37 +3015,37 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
         <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Z20" t="n">
         <v>1.91</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AB20" t="n">
         <v>1.37</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3123,58 +3123,58 @@
         <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="O21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
         <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,19 +3249,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="M22" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
         <v>3.25</v>
@@ -3270,28 +3270,28 @@
         <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
         <v>3.48</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
         <v>4.6</v>
@@ -3300,7 +3300,7 @@
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
         <v>1.69</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.83</v>
@@ -3396,13 +3396,13 @@
         <v>8.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
         <v>1.37</v>
@@ -3417,16 +3417,16 @@
         <v>3.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
         <v>2.38</v>
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="O24" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.24</v>
+        <v>3.09</v>
       </c>
       <c r="R24" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="T24" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
         <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="X24" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AB24" t="n">
         <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD24" t="n">
         <v>1.77</v>
@@ -3577,7 +3577,7 @@
         <v>1.39</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.09</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="R2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.36</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45946.375</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2106,25 +2106,25 @@
         <v>9.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y13" t="n">
         <v>2.05</v>
@@ -2133,16 +2133,16 @@
         <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AI13" t="n">
         <v>1.3</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.95</v>
@@ -2478,25 +2478,25 @@
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
         <v>2.15</v>
@@ -2520,16 +2520,16 @@
         <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AB16" t="n">
         <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,13 +2545,13 @@
         <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45946.51388888889</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O20" t="n">
         <v>5.05</v>
@@ -3030,10 +3030,10 @@
         <v>3.71</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
         <v>2.92</v>
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
         <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>2.94</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.31</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>2.39</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.1</v>
+        <v>3.09</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="X23" t="n">
-        <v>3.08</v>
+        <v>2.61</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.65</v>
+        <v>4.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.17</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.09</v>
+        <v>8.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.61</v>
+        <v>3.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>3.17</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45946.5</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2607,49 +2607,49 @@
         <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O17" t="n">
-        <v>5.32</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="Y17" t="n">
         <v>2.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="AB17" t="n">
         <v>1.2</v>
@@ -2658,7 +2658,7 @@
         <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" t="n">
         <v>2.87</v>
@@ -3003,22 +3003,22 @@
         <v>5.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
         <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.71</v>
+        <v>3.42</v>
       </c>
       <c r="Y20" t="n">
         <v>1.93</v>
@@ -3039,7 +3039,7 @@
         <v>2.92</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AC20" t="n">
         <v>1.82</v>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45946.60416666666</v>
@@ -3132,16 +3132,16 @@
         <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="T21" t="n">
         <v>2.6</v>
@@ -3153,10 +3153,10 @@
         <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="Y21" t="n">
         <v>1.8</v>
@@ -3168,13 +3168,13 @@
         <v>2.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
         <v>1.46</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45946.66666666666</v>
@@ -3297,7 +3297,7 @@
         <v>4.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC22" t="n">
         <v>2</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3387,10 +3387,10 @@
         <v>2.39</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
         <v>3.09</v>
@@ -3399,7 +3399,7 @@
         <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="T23" t="n">
         <v>3.4</v>
@@ -3408,13 +3408,13 @@
         <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X23" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="Y23" t="n">
         <v>2.17</v>
@@ -3423,16 +3423,16 @@
         <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.39</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
         <v>3.08</v>
@@ -3552,7 +3552,7 @@
         <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="AB24" t="n">
         <v>1.29</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.1</v>
+        <v>5.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T2" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AI2" t="n">
         <v>1.57</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45946.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.4</v>
+        <v>5.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="T20" t="n">
         <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
@@ -3027,13 +3027,13 @@
         <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AA20" t="n">
         <v>2.92</v>
@@ -3042,10 +3042,10 @@
         <v>1.31</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AI20" t="n">
         <v>2.6</v>
@@ -3120,31 +3120,31 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
         <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q21" t="n">
         <v>3.07</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
         <v>1.44</v>
@@ -3159,22 +3159,22 @@
         <v>3.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
         <v>2.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
         <v>1.46</v>
@@ -3249,58 +3249,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="N22" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
         <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
         <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
         <v>4.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AD22" t="n">
         <v>1.69</v>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AH22" t="n">
         <v>1.43</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45946.79166666666</v>
@@ -3378,31 +3378,31 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
         <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
         <v>1.32</v>
@@ -3411,28 +3411,28 @@
         <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X23" t="n">
         <v>2.54</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.17</v>
+        <v>2.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AA23" t="n">
         <v>4.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45946.89583333334</v>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
@@ -3537,25 +3537,25 @@
         <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
         <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AA24" t="n">
         <v>3.59</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
         <v>2.38</v>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45946.89583333334</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45946.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2613,52 +2613,52 @@
         <v>1.74</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>6.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="AB17" t="n">
         <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>2.77</v>
       </c>
       <c r="N22" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
         <v>3.5</v>
@@ -3264,34 +3264,34 @@
         <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="R22" t="n">
         <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
         <v>2.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
         <v>4.6</v>
@@ -3300,10 +3300,10 @@
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>2.15</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.8</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>2.54</v>
+        <v>3.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45946.89583333334</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.31</v>
+        <v>2.84</v>
       </c>
       <c r="M24" t="n">
-        <v>4.65</v>
+        <v>2.88</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>2.59</v>
       </c>
       <c r="O24" t="n">
-        <v>1.8</v>
+        <v>3.66</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="Z24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA24" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45946.89583333334</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.68</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45946.5</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2613,22 +2613,22 @@
         <v>1.74</v>
       </c>
       <c r="O17" t="n">
-        <v>6.42</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="R17" t="n">
         <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
         <v>1.26</v>
@@ -2637,28 +2637,28 @@
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
         <v>4.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI17" t="n">
         <v>2.87</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.57</v>
+        <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="O20" t="n">
         <v>5.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
         <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
         <v>2.92</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
         <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI20" t="n">
         <v>2.6</v>
@@ -3120,52 +3120,52 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
         <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AB21" t="n">
         <v>1.38</v>
@@ -3174,7 +3174,7 @@
         <v>1.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AI21" t="n">
         <v>2.1</v>
@@ -3249,49 +3249,49 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="M22" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="U22" t="n">
         <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
         <v>4.6</v>
@@ -3300,10 +3300,10 @@
         <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
         <v>1.41</v>
@@ -3378,16 +3378,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="P23" t="n">
         <v>2.17</v>
@@ -3399,31 +3399,31 @@
         <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
         <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X23" t="n">
         <v>3.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="AB23" t="n">
         <v>1.25</v>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AI23" t="n">
         <v>1.3</v>
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="O24" t="n">
         <v>3.66</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R24" t="n">
         <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
         <v>3.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
         <v>2.48</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AI24" t="n">
         <v>2.1</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -669,55 +669,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N2" t="n">
-        <v>4.75</v>
+        <v>4.97</v>
       </c>
       <c r="O2" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.52</v>
+        <v>5.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC2" t="n">
         <v>1.8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AI2" t="n">
         <v>1.57</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2290,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45946.5</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>2.97</v>
+        <v>7.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.53</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -665,65 +665,65 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>3.62</v>
+        <v>4.55</v>
       </c>
       <c r="N2" t="n">
-        <v>4.97</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -732,14 +732,14 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75', '86']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AI2" t="n">
         <v>1.57</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45946.41666666666</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45946.42361111111</v>
+        <v>45946.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.42361111111</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.45833333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>4.9</v>
+        <v>3.83</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="15">
@@ -2346,31 +2346,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
         <v>1.63</v>
@@ -2379,28 +2379,28 @@
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
         <v>1.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
         <v>1.7</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45946.51388888889</v>
+        <v>45946.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45946.52777777778</v>
+        <v>45946.51388888889</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45946.54166666666</v>
+        <v>45946.52777777778</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.4</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
-        <v>3.53</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.53</v>
+        <v>6.75</v>
       </c>
       <c r="O20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45946.60416666666</v>
+        <v>45946.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.47</v>
+        <v>5.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>3.53</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>1.53</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="P21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.24</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
         <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>4.14</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45946.66666666666</v>
+        <v>45946.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,86 +3249,86 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="N22" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="R22" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>3.19</v>
       </c>
       <c r="T22" t="n">
-        <v>3.48</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.25</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45946.79166666666</v>
+        <v>45946.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.34</v>
+        <v>2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>2.49</v>
       </c>
       <c r="O23" t="n">
-        <v>1.77</v>
+        <v>3.62</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.33</v>
+        <v>1.42</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45946.89583333334</v>
+        <v>45946.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,85 +3507,214 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.66</v>
+        <v>1.8</v>
       </c>
       <c r="P24" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.34</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45946.89583333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.43</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>2.48</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y25" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z25" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA24" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI24" t="n">
+      <c r="AA25" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI25" t="n">
         <v>2.1</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AJ25" t="n">
         <v>2.05</v>
       </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AK25" s="3" t="n">
         <v>45946.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45946.47916666666</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45946.48958333334</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,26 +2084,26 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,106 +2176,106 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '68', '83']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.47916666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,90 +2342,90 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>5.06</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.58</v>
+        <v>6.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>3.76</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>2.27</v>
       </c>
       <c r="Y15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.46</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>3.92</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45946.5</v>
+        <v>45946.48958333334</v>
       </c>
     </row>
     <row r="16">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,26 +2471,26 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45946.5</v>
@@ -2568,29 +2568,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2600,87 +2600,87 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45946.5</v>
@@ -2719,17 +2719,17 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2742,52 +2742,52 @@
         <v>1.74</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>5.51</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2796,14 +2796,14 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '36', '85']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" t="n">
         <v>2.87</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3120,52 +3120,52 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.4</v>
+        <v>4.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.53</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
         <v>2.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
         <v>2.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>4.14</v>
+        <v>3.58</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AB21" t="n">
         <v>1.33</v>
@@ -3174,7 +3174,7 @@
         <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
         <v>1.14</v>
@@ -3249,58 +3249,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD22" t="n">
         <v>2.1</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI22" t="n">
         <v>2.1</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>2.39</v>
       </c>
       <c r="O24" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>3.37</v>
+        <v>2.48</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.66</v>
+        <v>4.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.08</v>
+        <v>1.43</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45946.89583333334</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.39</v>
+        <v>7.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
         <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>2.48</v>
+        <v>3.37</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.88</v>
+        <v>3.66</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.43</v>
+        <v>3.08</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45946.89583333334</v>

--- a/jogos_2025-10-16.xlsx
+++ b/jogos_2025-10-16.xlsx
@@ -772,19 +772,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -794,87 +794,87 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45946.41666666666</v>
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -923,87 +923,87 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45946.41666666666</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,20 +3103,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '90+9']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '71']</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3232,20 +3232,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5', '90+3']</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="N23" t="n">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>3.62</v>
+        <v>4.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
         <v>2.15</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.01</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>2.51</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>7.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
         <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.88</v>
+        <v>3.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.43</v>
+        <v>3.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45946.89583333334</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>2.58</v>
       </c>
       <c r="O25" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>3.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
-        <v>3.37</v>
+        <v>2.64</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.94</v>
+        <v>2.64</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.66</v>
+        <v>5.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.08</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45946.89583333334</v>
